--- a/Kiem ke MT +PM Minh Thủy(Thống kê lại KASPER 3 nhà máy).xlsx
+++ b/Kiem ke MT +PM Minh Thủy(Thống kê lại KASPER 3 nhà máy).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="K:\DONG DUONG 1\IT\22.File\QUAN LY THIET BI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PHAN MEM QLY TBI IT(Đang làm 21-10-2025)\QUANLY-IT-Cai-Tien-Update-PM-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85DBB587-EBB5-41DB-ABE1-4177CB7DBE40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DDE3A7-4A12-4990-9434-66B952E30F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1778,7 +1778,7 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="101">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1964,6 +1964,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="3" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1974,10 +1981,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="3" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1987,9 +1990,18 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="3"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="3" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="3" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="3" builtinId="27"/>
@@ -3667,20 +3679,20 @@
       <c r="N38" s="61"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="86"/>
-      <c r="B39" s="86"/>
-      <c r="C39" s="86"/>
-      <c r="D39" s="86"/>
-      <c r="E39" s="86"/>
-      <c r="F39" s="86"/>
-      <c r="G39" s="86"/>
-      <c r="H39" s="86"/>
-      <c r="I39" s="86"/>
-      <c r="J39" s="86"/>
-      <c r="K39" s="86"/>
-      <c r="L39" s="86"/>
-      <c r="M39" s="86"/>
-      <c r="N39" s="86"/>
+      <c r="A39" s="91"/>
+      <c r="B39" s="91"/>
+      <c r="C39" s="91"/>
+      <c r="D39" s="91"/>
+      <c r="E39" s="91"/>
+      <c r="F39" s="91"/>
+      <c r="G39" s="91"/>
+      <c r="H39" s="91"/>
+      <c r="I39" s="91"/>
+      <c r="J39" s="91"/>
+      <c r="K39" s="91"/>
+      <c r="L39" s="91"/>
+      <c r="M39" s="91"/>
+      <c r="N39" s="91"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="13"/>
@@ -3699,11 +3711,11 @@
       <c r="N40" s="13"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="85" t="s">
+      <c r="A42" s="90" t="s">
         <v>139</v>
       </c>
-      <c r="B42" s="85"/>
-      <c r="C42" s="85"/>
+      <c r="B42" s="90"/>
+      <c r="C42" s="90"/>
       <c r="D42" s="20"/>
       <c r="E42" s="20"/>
       <c r="F42" s="57" t="s">
@@ -3712,9 +3724,9 @@
       <c r="G42" s="56">
         <v>3</v>
       </c>
-      <c r="I42" s="87"/>
-      <c r="J42" s="87"/>
-      <c r="K42" s="87"/>
+      <c r="I42" s="92"/>
+      <c r="J42" s="92"/>
+      <c r="K42" s="92"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
@@ -3925,11 +3937,11 @@
       <c r="C62" s="21"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="85" t="s">
+      <c r="A64" s="90" t="s">
         <v>141</v>
       </c>
-      <c r="B64" s="85"/>
-      <c r="C64" s="85"/>
+      <c r="B64" s="90"/>
+      <c r="C64" s="90"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="s">
@@ -6031,11 +6043,11 @@
       <c r="N55" s="61"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="85" t="s">
+      <c r="A58" s="90" t="s">
         <v>281</v>
       </c>
-      <c r="B58" s="85"/>
-      <c r="C58" s="85"/>
+      <c r="B58" s="90"/>
+      <c r="C58" s="90"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="24" t="s">
@@ -6198,11 +6210,11 @@
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="85" t="s">
+      <c r="A77" s="90" t="s">
         <v>283</v>
       </c>
-      <c r="B77" s="85"/>
-      <c r="C77" s="85"/>
+      <c r="B77" s="90"/>
+      <c r="C77" s="90"/>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="24" t="s">
@@ -6259,6 +6271,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7658CB2-1811-41FB-B4ED-2B208CC4F3B2}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A2:P100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6269,10 +6282,10 @@
     <col min="5" max="5" width="12.5703125" style="27" customWidth="1"/>
     <col min="6" max="6" width="18.85546875" style="27" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.5703125" style="27" customWidth="1"/>
-    <col min="8" max="8" width="30.7109375" style="27" customWidth="1"/>
+    <col min="8" max="8" width="31.140625" style="27" customWidth="1"/>
     <col min="9" max="9" width="17.140625" style="27" customWidth="1"/>
     <col min="10" max="10" width="15" style="27" customWidth="1"/>
-    <col min="11" max="11" width="21.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.85546875" style="27" customWidth="1"/>
     <col min="12" max="12" width="20.28515625" style="27" customWidth="1"/>
     <col min="13" max="13" width="18.42578125" style="27" customWidth="1"/>
     <col min="14" max="14" width="22.5703125" style="27" customWidth="1"/>
@@ -6325,7 +6338,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="77">
         <v>40</v>
       </c>
@@ -6365,7 +6378,7 @@
       </c>
       <c r="N3" s="77"/>
     </row>
-    <row r="4" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
         <v>46</v>
       </c>
@@ -6409,7 +6422,7 @@
       <c r="O4" s="26"/>
       <c r="P4" s="26"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="78">
         <v>47</v>
       </c>
@@ -6451,7 +6464,7 @@
       </c>
       <c r="N5" s="78"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="30">
         <v>48</v>
       </c>
@@ -6495,7 +6508,7 @@
       <c r="O6" s="31"/>
       <c r="P6" s="31"/>
     </row>
-    <row r="7" spans="1:16" s="31" customFormat="1" ht="75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" s="31" customFormat="1" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="43">
         <v>49</v>
       </c>
@@ -6539,7 +6552,7 @@
       <c r="O7" s="45"/>
       <c r="P7" s="45"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="26">
         <v>53</v>
       </c>
@@ -6579,7 +6592,7 @@
       </c>
       <c r="N8" s="26"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="26">
         <v>54</v>
       </c>
@@ -6621,7 +6634,7 @@
       </c>
       <c r="N9" s="26"/>
     </row>
-    <row r="10" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33">
         <v>55</v>
       </c>
@@ -6663,7 +6676,7 @@
       <c r="O10" s="47"/>
       <c r="P10" s="47"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="26">
         <v>64</v>
       </c>
@@ -6692,7 +6705,7 @@
       <c r="N11" s="26"/>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="30">
         <v>65</v>
       </c>
@@ -6722,7 +6735,7 @@
       <c r="O12" s="31"/>
       <c r="P12" s="11"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="26">
         <v>6</v>
       </c>
@@ -6760,7 +6773,7 @@
       </c>
       <c r="N13" s="26"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="26">
         <v>7</v>
       </c>
@@ -6796,7 +6809,7 @@
       </c>
       <c r="N14" s="26"/>
     </row>
-    <row r="15" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" s="59" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26">
         <v>9</v>
       </c>
@@ -6836,7 +6849,7 @@
       <c r="O15" s="27"/>
       <c r="P15" s="27"/>
     </row>
-    <row r="16" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" s="59" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="26">
         <v>10</v>
       </c>
@@ -6874,7 +6887,7 @@
       <c r="O16" s="27"/>
       <c r="P16" s="27"/>
     </row>
-    <row r="17" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" s="59" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26">
         <v>11</v>
       </c>
@@ -6912,7 +6925,7 @@
       <c r="O17" s="27"/>
       <c r="P17" s="27"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="26">
         <v>12</v>
       </c>
@@ -6948,7 +6961,7 @@
       </c>
       <c r="N18" s="26"/>
     </row>
-    <row r="19" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="26">
         <v>18</v>
       </c>
@@ -6986,7 +6999,7 @@
       <c r="O19" s="27"/>
       <c r="P19" s="27"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="26">
         <v>19</v>
       </c>
@@ -7022,7 +7035,7 @@
       </c>
       <c r="N20" s="26"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="26">
         <v>20</v>
       </c>
@@ -7058,7 +7071,7 @@
       </c>
       <c r="N21" s="26"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="26">
         <v>35</v>
       </c>
@@ -7098,7 +7111,7 @@
       </c>
       <c r="N22" s="26"/>
     </row>
-    <row r="23" spans="1:16" s="41" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" s="41" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="26">
         <v>67</v>
       </c>
@@ -7128,7 +7141,7 @@
       <c r="O23" s="27"/>
       <c r="P23" s="27"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="26">
         <v>41</v>
       </c>
@@ -7168,7 +7181,7 @@
       </c>
       <c r="N24" s="26"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="30">
         <v>44</v>
       </c>
@@ -7210,7 +7223,7 @@
       <c r="O25" s="84"/>
       <c r="P25" s="31"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="26">
         <v>50</v>
       </c>
@@ -7251,7 +7264,7 @@
       <c r="N26" s="26"/>
       <c r="O26" s="83"/>
     </row>
-    <row r="27" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="26">
         <v>51</v>
       </c>
@@ -7293,7 +7306,7 @@
       <c r="O27" s="26"/>
       <c r="P27" s="27"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="26">
         <v>52</v>
       </c>
@@ -7333,7 +7346,7 @@
       </c>
       <c r="N28" s="26"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="26">
         <v>1</v>
       </c>
@@ -7373,7 +7386,7 @@
       </c>
       <c r="N29" s="26"/>
     </row>
-    <row r="30" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="30">
         <v>28</v>
       </c>
@@ -7413,7 +7426,7 @@
       </c>
       <c r="N30" s="30"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="26">
         <v>29</v>
       </c>
@@ -7455,7 +7468,7 @@
       <c r="O31" s="31"/>
       <c r="P31" s="31"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="26">
         <v>37</v>
       </c>
@@ -7495,7 +7508,7 @@
       </c>
       <c r="N32" s="26"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="26">
         <v>39</v>
       </c>
@@ -7535,7 +7548,7 @@
       </c>
       <c r="N33" s="26"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="77">
         <v>42</v>
       </c>
@@ -7575,7 +7588,7 @@
       </c>
       <c r="N34" s="77"/>
     </row>
-    <row r="35" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="26">
         <v>43</v>
       </c>
@@ -7613,7 +7626,7 @@
       <c r="O35" s="26"/>
       <c r="P35" s="26"/>
     </row>
-    <row r="36" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="26">
         <v>45</v>
       </c>
@@ -7651,7 +7664,7 @@
       <c r="O36" s="26"/>
       <c r="P36" s="26"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="78">
         <v>58</v>
       </c>
@@ -7687,7 +7700,7 @@
       </c>
       <c r="N37" s="78"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="26">
         <v>59</v>
       </c>
@@ -7723,7 +7736,7 @@
       </c>
       <c r="N38" s="26"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="26">
         <v>60</v>
       </c>
@@ -7759,7 +7772,7 @@
       </c>
       <c r="N39" s="26"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="26">
         <v>63</v>
       </c>
@@ -7799,7 +7812,7 @@
       </c>
       <c r="N40" s="26"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>2</v>
       </c>
@@ -7831,7 +7844,7 @@
       <c r="O41" s="11"/>
       <c r="P41" s="11"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="30">
         <v>5</v>
       </c>
@@ -7871,7 +7884,7 @@
       <c r="O42" s="31"/>
       <c r="P42" s="31"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="30">
         <v>17</v>
       </c>
@@ -7953,7 +7966,7 @@
       <c r="O44" s="41"/>
       <c r="P44" s="41"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="26">
         <v>22</v>
       </c>
@@ -7989,7 +8002,7 @@
       </c>
       <c r="N45" s="26"/>
     </row>
-    <row r="46" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="26">
         <v>23</v>
       </c>
@@ -8027,7 +8040,7 @@
       <c r="O46" s="82"/>
       <c r="P46" s="27"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="26">
         <v>24</v>
       </c>
@@ -8068,7 +8081,7 @@
       <c r="N47" s="30"/>
       <c r="O47" s="82"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="30">
         <v>25</v>
       </c>
@@ -8108,7 +8121,7 @@
       <c r="O48" s="81"/>
       <c r="P48" s="31"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="26">
         <v>26</v>
       </c>
@@ -8144,7 +8157,7 @@
       </c>
       <c r="N49" s="26"/>
     </row>
-    <row r="50" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="26">
         <v>27</v>
       </c>
@@ -8182,7 +8195,7 @@
       <c r="O50" s="27"/>
       <c r="P50" s="27"/>
     </row>
-    <row r="51" spans="1:16" s="45" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" s="45" customFormat="1" ht="71.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="26">
         <v>36</v>
       </c>
@@ -8224,7 +8237,7 @@
       <c r="O51" s="27"/>
       <c r="P51" s="27"/>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="30">
         <v>68</v>
       </c>
@@ -8252,7 +8265,7 @@
       </c>
       <c r="N52" s="30"/>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="26">
         <v>3</v>
       </c>
@@ -8290,7 +8303,7 @@
       </c>
       <c r="N53" s="26"/>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="26">
         <v>30</v>
       </c>
@@ -8330,7 +8343,7 @@
       </c>
       <c r="N54" s="26"/>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="26">
         <v>31</v>
       </c>
@@ -8370,7 +8383,7 @@
       </c>
       <c r="N55" s="26"/>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="26">
         <v>32</v>
       </c>
@@ -8408,7 +8421,7 @@
       </c>
       <c r="N56" s="26"/>
     </row>
-    <row r="57" spans="1:16" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" s="47" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="26">
         <v>56</v>
       </c>
@@ -8450,7 +8463,7 @@
       <c r="O57" s="27"/>
       <c r="P57" s="27"/>
     </row>
-    <row r="58" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="43">
         <v>57</v>
       </c>
@@ -8493,7 +8506,7 @@
       <c r="N58" s="26"/>
       <c r="O58" s="50"/>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="30">
         <v>62</v>
       </c>
@@ -8535,41 +8548,41 @@
       <c r="O59" s="30"/>
       <c r="P59" s="31"/>
     </row>
-    <row r="60" spans="1:16" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="89"/>
-      <c r="B60" s="89" t="s">
+    <row r="60" spans="1:16" s="87" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="85"/>
+      <c r="B60" s="85" t="s">
         <v>81</v>
       </c>
-      <c r="C60" s="90" t="s">
+      <c r="C60" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="90" t="s">
+      <c r="D60" s="86" t="s">
         <v>485</v>
       </c>
-      <c r="E60" s="89" t="s">
+      <c r="E60" s="85" t="s">
         <v>285</v>
       </c>
-      <c r="F60" s="89" t="s">
+      <c r="F60" s="85" t="s">
         <v>486</v>
       </c>
-      <c r="G60" s="89" t="s">
+      <c r="G60" s="85" t="s">
         <v>487</v>
       </c>
-      <c r="H60" s="91" t="s">
+      <c r="H60" s="94" t="s">
         <v>495</v>
       </c>
-      <c r="I60" s="92"/>
-      <c r="J60" s="93"/>
-      <c r="K60" s="89"/>
-      <c r="L60" s="90" t="s">
+      <c r="I60" s="95"/>
+      <c r="J60" s="96"/>
+      <c r="K60" s="85"/>
+      <c r="L60" s="86" t="s">
         <v>440</v>
       </c>
-      <c r="M60" s="89" t="s">
+      <c r="M60" s="85" t="s">
         <v>24</v>
       </c>
-      <c r="N60" s="89"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N60" s="85"/>
+    </row>
+    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="57">
         <v>13</v>
       </c>
@@ -8607,7 +8620,7 @@
       <c r="O61" s="59"/>
       <c r="P61" s="59"/>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="57">
         <v>14</v>
       </c>
@@ -8645,7 +8658,7 @@
       <c r="O62" s="59"/>
       <c r="P62" s="59"/>
     </row>
-    <row r="63" spans="1:16" s="47" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" s="47" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="57">
         <v>15</v>
       </c>
@@ -8685,7 +8698,7 @@
       <c r="O63" s="59"/>
       <c r="P63" s="59"/>
     </row>
-    <row r="64" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="26">
         <v>16</v>
       </c>
@@ -8723,7 +8736,7 @@
       <c r="O64" s="27"/>
       <c r="P64" s="27"/>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="26">
         <v>38</v>
       </c>
@@ -8763,7 +8776,7 @@
       </c>
       <c r="N65" s="26"/>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="26">
         <v>66</v>
       </c>
@@ -8792,7 +8805,7 @@
       <c r="N66" s="26"/>
       <c r="P66" s="11"/>
     </row>
-    <row r="67" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="26">
         <v>4</v>
       </c>
@@ -8834,7 +8847,7 @@
       <c r="O67" s="27"/>
       <c r="P67" s="27"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="30">
         <v>8</v>
       </c>
@@ -8872,7 +8885,7 @@
       <c r="O68" s="31"/>
       <c r="P68" s="31"/>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="33">
         <v>61</v>
       </c>
@@ -8914,7 +8927,7 @@
       <c r="O69" s="47"/>
       <c r="P69" s="47"/>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="26">
         <v>69</v>
       </c>
@@ -8942,7 +8955,7 @@
       </c>
       <c r="N70" s="26"/>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>33</v>
       </c>
@@ -8970,7 +8983,7 @@
       <c r="O71" s="11"/>
       <c r="P71" s="11"/>
     </row>
-    <row r="72" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" s="59" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>34</v>
       </c>
@@ -8998,37 +9011,37 @@
       <c r="O72" s="11"/>
       <c r="P72" s="11"/>
     </row>
-    <row r="73" spans="1:16" s="94" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="95"/>
-      <c r="B73" s="96"/>
-      <c r="C73" s="96" t="s">
+    <row r="73" spans="1:16" s="87" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="88"/>
+      <c r="B73" s="89"/>
+      <c r="C73" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="D73" s="96" t="s">
+      <c r="D73" s="89" t="s">
         <v>489</v>
       </c>
-      <c r="E73" s="89" t="s">
+      <c r="E73" s="85" t="s">
         <v>285</v>
       </c>
-      <c r="F73" s="96" t="s">
+      <c r="F73" s="89" t="s">
         <v>490</v>
       </c>
-      <c r="G73" s="96" t="s">
+      <c r="G73" s="89" t="s">
         <v>491</v>
       </c>
-      <c r="H73" s="91" t="s">
+      <c r="H73" s="94" t="s">
         <v>495</v>
       </c>
-      <c r="I73" s="92"/>
-      <c r="J73" s="93"/>
-      <c r="K73" s="89"/>
-      <c r="L73" s="89" t="s">
+      <c r="I73" s="95"/>
+      <c r="J73" s="96"/>
+      <c r="K73" s="85"/>
+      <c r="L73" s="85" t="s">
         <v>488</v>
       </c>
-      <c r="M73" s="89" t="s">
+      <c r="M73" s="85" t="s">
         <v>389</v>
       </c>
-      <c r="N73" s="95"/>
+      <c r="N73" s="88"/>
     </row>
     <row r="74" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A74"/>
@@ -9085,11 +9098,11 @@
       <c r="P76"/>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A77" s="88" t="s">
+      <c r="A77" s="93" t="s">
         <v>461</v>
       </c>
-      <c r="B77" s="88"/>
-      <c r="C77" s="88"/>
+      <c r="B77" s="93"/>
+      <c r="C77" s="93"/>
       <c r="D77"/>
       <c r="E77"/>
       <c r="F77"/>
@@ -9142,8 +9155,13 @@
       <c r="C80" s="16">
         <v>2</v>
       </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="J80" s="49"/>
+      <c r="K80" s="49"/>
+      <c r="L80" s="49"/>
+      <c r="M80" s="49"/>
+      <c r="N80" s="49"/>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="16">
         <v>3</v>
       </c>
@@ -9153,8 +9171,13 @@
       <c r="C81" s="16">
         <v>12</v>
       </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="J81" s="49"/>
+      <c r="K81" s="49"/>
+      <c r="L81" s="97"/>
+      <c r="M81" s="49"/>
+      <c r="N81" s="49"/>
+    </row>
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="16">
         <v>4</v>
       </c>
@@ -9164,8 +9187,13 @@
       <c r="C82" s="16">
         <v>17</v>
       </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="J82" s="49"/>
+      <c r="K82" s="49"/>
+      <c r="L82" s="49"/>
+      <c r="M82" s="49"/>
+      <c r="N82" s="49"/>
+    </row>
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="16">
         <v>5</v>
       </c>
@@ -9175,8 +9203,13 @@
       <c r="C83" s="16">
         <v>27</v>
       </c>
-    </row>
-    <row r="84" spans="1:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J83" s="98"/>
+      <c r="K83" s="98"/>
+      <c r="L83" s="99"/>
+      <c r="M83" s="49"/>
+      <c r="N83" s="49"/>
+    </row>
+    <row r="84" spans="1:14" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="35"/>
       <c r="B84" s="76" t="s">
         <v>484</v>
@@ -9185,26 +9218,46 @@
         <f>SUM(C79:C83)</f>
         <v>63</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="J84" s="49"/>
+      <c r="K84" s="49"/>
+      <c r="L84" s="49"/>
+      <c r="M84" s="49"/>
+      <c r="N84" s="49"/>
+    </row>
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="35"/>
       <c r="B85"/>
       <c r="C85"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="J85" s="49"/>
+      <c r="K85" s="49"/>
+      <c r="L85" s="49"/>
+      <c r="M85" s="49"/>
+      <c r="N85" s="49"/>
+    </row>
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="35"/>
       <c r="B86"/>
       <c r="C86"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A87" s="85" t="s">
+      <c r="J86" s="49"/>
+      <c r="K86" s="49"/>
+      <c r="L86" s="49"/>
+      <c r="M86" s="49"/>
+      <c r="N86" s="49"/>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A87" s="90" t="s">
         <v>462</v>
       </c>
-      <c r="B87" s="85"/>
-      <c r="C87" s="85"/>
+      <c r="B87" s="90"/>
+      <c r="C87" s="90"/>
       <c r="D87" s="54"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="J87" s="49"/>
+      <c r="K87" s="49"/>
+      <c r="L87" s="49"/>
+      <c r="M87" s="49"/>
+      <c r="N87" s="49"/>
+    </row>
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="52" t="s">
         <v>70</v>
       </c>
@@ -9215,8 +9268,13 @@
         <v>137</v>
       </c>
       <c r="D88" s="55"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="J88" s="49"/>
+      <c r="K88" s="49"/>
+      <c r="L88" s="49"/>
+      <c r="M88" s="100"/>
+      <c r="N88" s="49"/>
+    </row>
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="16">
         <v>1</v>
       </c>
@@ -9227,8 +9285,13 @@
         <v>53</v>
       </c>
       <c r="D89" s="49"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="J89" s="49"/>
+      <c r="K89" s="49"/>
+      <c r="L89" s="49"/>
+      <c r="M89" s="49"/>
+      <c r="N89" s="49"/>
+    </row>
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="16">
         <v>2</v>
       </c>
@@ -9239,8 +9302,12 @@
         <v>5</v>
       </c>
       <c r="D90" s="49"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G90" s="49"/>
+      <c r="H90" s="49"/>
+      <c r="I90" s="49"/>
+      <c r="J90" s="49"/>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="16">
         <v>3</v>
       </c>
@@ -9251,8 +9318,12 @@
         <v>51</v>
       </c>
       <c r="D91" s="49"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G91" s="49"/>
+      <c r="H91" s="49"/>
+      <c r="I91" s="49"/>
+      <c r="J91" s="49"/>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="16">
         <v>4</v>
       </c>
@@ -9263,8 +9334,12 @@
         <v>1</v>
       </c>
       <c r="D92" s="49"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G92" s="49"/>
+      <c r="H92" s="97"/>
+      <c r="I92" s="49"/>
+      <c r="J92" s="49"/>
+    </row>
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="16">
         <v>5</v>
       </c>
@@ -9275,8 +9350,12 @@
         <v>39</v>
       </c>
       <c r="D93" s="49"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G93" s="49"/>
+      <c r="H93" s="49"/>
+      <c r="I93" s="49"/>
+      <c r="J93" s="49"/>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="16">
         <v>6</v>
       </c>
@@ -9287,19 +9366,27 @@
         <v>18</v>
       </c>
       <c r="D94" s="49"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G94" s="49"/>
+      <c r="H94" s="49"/>
+      <c r="I94" s="99"/>
+      <c r="J94" s="49"/>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="37"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="G95" s="49"/>
+      <c r="H95" s="49"/>
+      <c r="I95" s="49"/>
+      <c r="J95" s="49"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="37"/>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="85" t="s">
+      <c r="A97" s="90" t="s">
         <v>463</v>
       </c>
-      <c r="B97" s="85"/>
-      <c r="C97" s="85"/>
+      <c r="B97" s="90"/>
+      <c r="C97" s="90"/>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="24" t="s">
@@ -9336,6 +9423,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:R73" xr:uid="{F96D30D7-88C4-4D8B-8E01-9968623D733C}">
+    <filterColumn colId="10">
+      <filters>
+        <filter val="SOLID WORDS 2022_x000a_ROBOTCUT-CAM_x000a_DISPRO SOLID FOR EDM"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P72">
       <sortCondition ref="M2:M72"/>
     </sortState>

--- a/Kiem ke MT +PM Minh Thủy(Thống kê lại KASPER 3 nhà máy).xlsx
+++ b/Kiem ke MT +PM Minh Thủy(Thống kê lại KASPER 3 nhà máy).xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PHAN MEM QLY TBI IT(Đang làm 21-10-2025)\QUANLY-IT-Cai-Tien-Update-PM-\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PHAN MEM QLY TBI IT(Đang làm 22-10-2025)\QUANLY-IT-Cai-Tien-Update-PM-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6DDE3A7-4A12-4990-9434-66B952E30F92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DFB5FE-D503-4C95-8676-1C6456F9EB69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DD1" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="DDK" sheetId="4" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DD1'!$A$2:$N$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DD1'!$A$2:$N$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">DDK!$A$2:$R$73</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -1778,7 +1778,7 @@
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1971,13 +1971,22 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="3" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1989,18 +1998,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="6" borderId="7" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2285,6 +2282,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5006B91-DE22-424D-8A0F-6DF1B14267DE}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A2:N67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2294,8 +2292,8 @@
     <col min="5" max="5" width="19.85546875" customWidth="1"/>
     <col min="6" max="6" width="31.7109375" customWidth="1"/>
     <col min="7" max="7" width="22.28515625" customWidth="1"/>
-    <col min="8" max="8" width="19.42578125" customWidth="1"/>
-    <col min="9" max="9" width="13.140625" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" customWidth="1"/>
+    <col min="9" max="9" width="15.5703125" customWidth="1"/>
     <col min="10" max="10" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="14.42578125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="23" customWidth="1"/>
@@ -2346,7 +2344,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -2386,7 +2384,7 @@
       </c>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
         <v>2</v>
       </c>
@@ -2426,7 +2424,7 @@
       </c>
       <c r="N4" s="5"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>3</v>
       </c>
@@ -2466,7 +2464,7 @@
       </c>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>4</v>
       </c>
@@ -2506,7 +2504,7 @@
       </c>
       <c r="N6" s="1"/>
     </row>
-    <row r="7" spans="1:14" s="67" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" s="67" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="64">
         <v>5</v>
       </c>
@@ -2546,7 +2544,7 @@
       </c>
       <c r="N7" s="65"/>
     </row>
-    <row r="8" spans="1:14" s="67" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" s="67" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="64">
         <v>6</v>
       </c>
@@ -2586,7 +2584,7 @@
       </c>
       <c r="N8" s="65"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>7</v>
       </c>
@@ -2626,7 +2624,7 @@
       </c>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>8</v>
       </c>
@@ -2666,7 +2664,7 @@
       </c>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>9</v>
       </c>
@@ -2706,7 +2704,7 @@
       </c>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12">
         <v>10</v>
       </c>
@@ -2746,7 +2744,7 @@
       </c>
       <c r="N12" s="5"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>11</v>
       </c>
@@ -2786,7 +2784,7 @@
       </c>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
         <v>12</v>
       </c>
@@ -2826,7 +2824,7 @@
       </c>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>13</v>
       </c>
@@ -2866,7 +2864,7 @@
       </c>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
         <v>14</v>
       </c>
@@ -2906,7 +2904,7 @@
       </c>
       <c r="N16" s="5"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>15</v>
       </c>
@@ -2946,7 +2944,7 @@
       </c>
       <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12">
         <v>16</v>
       </c>
@@ -2986,7 +2984,7 @@
       </c>
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>17</v>
       </c>
@@ -3026,7 +3024,7 @@
       </c>
       <c r="N19" s="1"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12">
         <v>18</v>
       </c>
@@ -3066,7 +3064,7 @@
       </c>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>19</v>
       </c>
@@ -3106,7 +3104,7 @@
       </c>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="68">
         <v>20</v>
       </c>
@@ -3146,7 +3144,7 @@
       </c>
       <c r="N22" s="69"/>
     </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3184,7 +3182,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3222,7 +3220,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="72">
         <v>23</v>
       </c>
@@ -3262,7 +3260,7 @@
       </c>
       <c r="N25" s="73"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
         <v>24</v>
       </c>
@@ -3302,7 +3300,7 @@
       </c>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>25</v>
       </c>
@@ -3342,7 +3340,7 @@
       </c>
       <c r="N27" s="1"/>
     </row>
-    <row r="28" spans="1:14" s="59" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" s="59" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="56">
         <v>26</v>
       </c>
@@ -3454,7 +3452,7 @@
       </c>
       <c r="N30" s="57"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="60">
         <v>29</v>
       </c>
@@ -3482,7 +3480,7 @@
       </c>
       <c r="N31" s="61"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="60">
         <v>30</v>
       </c>
@@ -3510,7 +3508,7 @@
       </c>
       <c r="N32" s="61"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="60">
         <v>31</v>
       </c>
@@ -3538,7 +3536,7 @@
       </c>
       <c r="N33" s="61"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="60">
         <v>32</v>
       </c>
@@ -3566,7 +3564,7 @@
       </c>
       <c r="N34" s="61"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="60">
         <v>33</v>
       </c>
@@ -3594,7 +3592,7 @@
       </c>
       <c r="N35" s="61"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="60">
         <v>34</v>
       </c>
@@ -3622,7 +3620,7 @@
       </c>
       <c r="N36" s="61"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="60">
         <v>35</v>
       </c>
@@ -3650,7 +3648,7 @@
       </c>
       <c r="N37" s="61"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="60">
         <v>36</v>
       </c>
@@ -3679,20 +3677,20 @@
       <c r="N38" s="61"/>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A39" s="91"/>
-      <c r="B39" s="91"/>
-      <c r="C39" s="91"/>
-      <c r="D39" s="91"/>
-      <c r="E39" s="91"/>
-      <c r="F39" s="91"/>
-      <c r="G39" s="91"/>
-      <c r="H39" s="91"/>
-      <c r="I39" s="91"/>
-      <c r="J39" s="91"/>
-      <c r="K39" s="91"/>
-      <c r="L39" s="91"/>
-      <c r="M39" s="91"/>
-      <c r="N39" s="91"/>
+      <c r="A39" s="95"/>
+      <c r="B39" s="95"/>
+      <c r="C39" s="95"/>
+      <c r="D39" s="95"/>
+      <c r="E39" s="95"/>
+      <c r="F39" s="95"/>
+      <c r="G39" s="95"/>
+      <c r="H39" s="95"/>
+      <c r="I39" s="95"/>
+      <c r="J39" s="95"/>
+      <c r="K39" s="95"/>
+      <c r="L39" s="95"/>
+      <c r="M39" s="95"/>
+      <c r="N39" s="95"/>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="13"/>
@@ -3711,11 +3709,11 @@
       <c r="N40" s="13"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A42" s="90" t="s">
+      <c r="A42" s="94" t="s">
         <v>139</v>
       </c>
-      <c r="B42" s="90"/>
-      <c r="C42" s="90"/>
+      <c r="B42" s="94"/>
+      <c r="C42" s="94"/>
       <c r="D42" s="20"/>
       <c r="E42" s="20"/>
       <c r="F42" s="57" t="s">
@@ -3724,9 +3722,9 @@
       <c r="G42" s="56">
         <v>3</v>
       </c>
-      <c r="I42" s="92"/>
-      <c r="J42" s="92"/>
-      <c r="K42" s="92"/>
+      <c r="I42" s="54"/>
+      <c r="J42" s="54"/>
+      <c r="K42" s="54"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="9" t="s">
@@ -3937,11 +3935,11 @@
       <c r="C62" s="21"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="90" t="s">
+      <c r="A64" s="94" t="s">
         <v>141</v>
       </c>
-      <c r="B64" s="90"/>
-      <c r="C64" s="90"/>
+      <c r="B64" s="94"/>
+      <c r="C64" s="94"/>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="9" t="s">
@@ -3977,11 +3975,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N2" xr:uid="{083D8963-DEF1-4333-BE50-8D9BD074B1F1}"/>
-  <mergeCells count="4">
+  <autoFilter ref="A2:N38" xr:uid="{083D8963-DEF1-4333-BE50-8D9BD074B1F1}">
+    <filterColumn colId="12">
+      <filters>
+        <filter val="IT"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <mergeCells count="3">
     <mergeCell ref="A64:C64"/>
     <mergeCell ref="A39:N39"/>
-    <mergeCell ref="I42:K42"/>
     <mergeCell ref="A42:C42"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6043,11 +6046,11 @@
       <c r="N55" s="61"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A58" s="90" t="s">
+      <c r="A58" s="94" t="s">
         <v>281</v>
       </c>
-      <c r="B58" s="90"/>
-      <c r="C58" s="90"/>
+      <c r="B58" s="94"/>
+      <c r="C58" s="94"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="24" t="s">
@@ -6210,11 +6213,11 @@
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" s="90" t="s">
+      <c r="A77" s="94" t="s">
         <v>283</v>
       </c>
-      <c r="B77" s="90"/>
-      <c r="C77" s="90"/>
+      <c r="B77" s="94"/>
+      <c r="C77" s="94"/>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="24" t="s">
@@ -6271,7 +6274,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7658CB2-1811-41FB-B4ED-2B208CC4F3B2}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A2:P100"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6338,7 +6340,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="77">
         <v>40</v>
       </c>
@@ -6378,7 +6380,7 @@
       </c>
       <c r="N3" s="77"/>
     </row>
-    <row r="4" spans="1:16" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
         <v>46</v>
       </c>
@@ -6422,7 +6424,7 @@
       <c r="O4" s="26"/>
       <c r="P4" s="26"/>
     </row>
-    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="78">
         <v>47</v>
       </c>
@@ -6464,7 +6466,7 @@
       </c>
       <c r="N5" s="78"/>
     </row>
-    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="30">
         <v>48</v>
       </c>
@@ -6508,7 +6510,7 @@
       <c r="O6" s="31"/>
       <c r="P6" s="31"/>
     </row>
-    <row r="7" spans="1:16" s="31" customFormat="1" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" s="31" customFormat="1" ht="75" x14ac:dyDescent="0.25">
       <c r="A7" s="43">
         <v>49</v>
       </c>
@@ -6552,7 +6554,7 @@
       <c r="O7" s="45"/>
       <c r="P7" s="45"/>
     </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="26">
         <v>53</v>
       </c>
@@ -6592,7 +6594,7 @@
       </c>
       <c r="N8" s="26"/>
     </row>
-    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="26">
         <v>54</v>
       </c>
@@ -6634,7 +6636,7 @@
       </c>
       <c r="N9" s="26"/>
     </row>
-    <row r="10" spans="1:16" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="33">
         <v>55</v>
       </c>
@@ -6676,7 +6678,7 @@
       <c r="O10" s="47"/>
       <c r="P10" s="47"/>
     </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="26">
         <v>64</v>
       </c>
@@ -6705,7 +6707,7 @@
       <c r="N11" s="26"/>
       <c r="P11" s="11"/>
     </row>
-    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="30">
         <v>65</v>
       </c>
@@ -6735,7 +6737,7 @@
       <c r="O12" s="31"/>
       <c r="P12" s="11"/>
     </row>
-    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="26">
         <v>6</v>
       </c>
@@ -6773,7 +6775,7 @@
       </c>
       <c r="N13" s="26"/>
     </row>
-    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="26">
         <v>7</v>
       </c>
@@ -6809,7 +6811,7 @@
       </c>
       <c r="N14" s="26"/>
     </row>
-    <row r="15" spans="1:16" s="59" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="26">
         <v>9</v>
       </c>
@@ -6849,7 +6851,7 @@
       <c r="O15" s="27"/>
       <c r="P15" s="27"/>
     </row>
-    <row r="16" spans="1:16" s="59" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="26">
         <v>10</v>
       </c>
@@ -6887,7 +6889,7 @@
       <c r="O16" s="27"/>
       <c r="P16" s="27"/>
     </row>
-    <row r="17" spans="1:16" s="59" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="26">
         <v>11</v>
       </c>
@@ -6925,7 +6927,7 @@
       <c r="O17" s="27"/>
       <c r="P17" s="27"/>
     </row>
-    <row r="18" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="26">
         <v>12</v>
       </c>
@@ -6961,7 +6963,7 @@
       </c>
       <c r="N18" s="26"/>
     </row>
-    <row r="19" spans="1:16" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="26">
         <v>18</v>
       </c>
@@ -6999,7 +7001,7 @@
       <c r="O19" s="27"/>
       <c r="P19" s="27"/>
     </row>
-    <row r="20" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="26">
         <v>19</v>
       </c>
@@ -7035,7 +7037,7 @@
       </c>
       <c r="N20" s="26"/>
     </row>
-    <row r="21" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="26">
         <v>20</v>
       </c>
@@ -7071,7 +7073,7 @@
       </c>
       <c r="N21" s="26"/>
     </row>
-    <row r="22" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="26">
         <v>35</v>
       </c>
@@ -7111,7 +7113,7 @@
       </c>
       <c r="N22" s="26"/>
     </row>
-    <row r="23" spans="1:16" s="41" customFormat="1" ht="26.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" s="41" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="26">
         <v>67</v>
       </c>
@@ -7141,7 +7143,7 @@
       <c r="O23" s="27"/>
       <c r="P23" s="27"/>
     </row>
-    <row r="24" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="26">
         <v>41</v>
       </c>
@@ -7181,7 +7183,7 @@
       </c>
       <c r="N24" s="26"/>
     </row>
-    <row r="25" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="30">
         <v>44</v>
       </c>
@@ -7223,7 +7225,7 @@
       <c r="O25" s="84"/>
       <c r="P25" s="31"/>
     </row>
-    <row r="26" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="26">
         <v>50</v>
       </c>
@@ -7264,7 +7266,7 @@
       <c r="N26" s="26"/>
       <c r="O26" s="83"/>
     </row>
-    <row r="27" spans="1:16" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="26">
         <v>51</v>
       </c>
@@ -7306,7 +7308,7 @@
       <c r="O27" s="26"/>
       <c r="P27" s="27"/>
     </row>
-    <row r="28" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="26">
         <v>52</v>
       </c>
@@ -7346,7 +7348,7 @@
       </c>
       <c r="N28" s="26"/>
     </row>
-    <row r="29" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="26">
         <v>1</v>
       </c>
@@ -7386,7 +7388,7 @@
       </c>
       <c r="N29" s="26"/>
     </row>
-    <row r="30" spans="1:16" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="30">
         <v>28</v>
       </c>
@@ -7426,7 +7428,7 @@
       </c>
       <c r="N30" s="30"/>
     </row>
-    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="26">
         <v>29</v>
       </c>
@@ -7468,7 +7470,7 @@
       <c r="O31" s="31"/>
       <c r="P31" s="31"/>
     </row>
-    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="26">
         <v>37</v>
       </c>
@@ -7508,7 +7510,7 @@
       </c>
       <c r="N32" s="26"/>
     </row>
-    <row r="33" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="26">
         <v>39</v>
       </c>
@@ -7548,7 +7550,7 @@
       </c>
       <c r="N33" s="26"/>
     </row>
-    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="77">
         <v>42</v>
       </c>
@@ -7588,7 +7590,7 @@
       </c>
       <c r="N34" s="77"/>
     </row>
-    <row r="35" spans="1:16" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="26">
         <v>43</v>
       </c>
@@ -7626,7 +7628,7 @@
       <c r="O35" s="26"/>
       <c r="P35" s="26"/>
     </row>
-    <row r="36" spans="1:16" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A36" s="26">
         <v>45</v>
       </c>
@@ -7664,7 +7666,7 @@
       <c r="O36" s="26"/>
       <c r="P36" s="26"/>
     </row>
-    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="78">
         <v>58</v>
       </c>
@@ -7700,7 +7702,7 @@
       </c>
       <c r="N37" s="78"/>
     </row>
-    <row r="38" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="26">
         <v>59</v>
       </c>
@@ -7736,7 +7738,7 @@
       </c>
       <c r="N38" s="26"/>
     </row>
-    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="26">
         <v>60</v>
       </c>
@@ -7772,7 +7774,7 @@
       </c>
       <c r="N39" s="26"/>
     </row>
-    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="26">
         <v>63</v>
       </c>
@@ -7812,7 +7814,7 @@
       </c>
       <c r="N40" s="26"/>
     </row>
-    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
         <v>2</v>
       </c>
@@ -7844,7 +7846,7 @@
       <c r="O41" s="11"/>
       <c r="P41" s="11"/>
     </row>
-    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="30">
         <v>5</v>
       </c>
@@ -7884,7 +7886,7 @@
       <c r="O42" s="31"/>
       <c r="P42" s="31"/>
     </row>
-    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="30">
         <v>17</v>
       </c>
@@ -7926,7 +7928,7 @@
       <c r="O43" s="31"/>
       <c r="P43" s="31"/>
     </row>
-    <row r="44" spans="1:16" ht="60" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A44" s="38">
         <v>21</v>
       </c>
@@ -7966,7 +7968,7 @@
       <c r="O44" s="41"/>
       <c r="P44" s="41"/>
     </row>
-    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="26">
         <v>22</v>
       </c>
@@ -8002,7 +8004,7 @@
       </c>
       <c r="N45" s="26"/>
     </row>
-    <row r="46" spans="1:16" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A46" s="26">
         <v>23</v>
       </c>
@@ -8040,7 +8042,7 @@
       <c r="O46" s="82"/>
       <c r="P46" s="27"/>
     </row>
-    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="26">
         <v>24</v>
       </c>
@@ -8081,7 +8083,7 @@
       <c r="N47" s="30"/>
       <c r="O47" s="82"/>
     </row>
-    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="30">
         <v>25</v>
       </c>
@@ -8121,7 +8123,7 @@
       <c r="O48" s="81"/>
       <c r="P48" s="31"/>
     </row>
-    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="26">
         <v>26</v>
       </c>
@@ -8157,7 +8159,7 @@
       </c>
       <c r="N49" s="26"/>
     </row>
-    <row r="50" spans="1:16" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A50" s="26">
         <v>27</v>
       </c>
@@ -8195,7 +8197,7 @@
       <c r="O50" s="27"/>
       <c r="P50" s="27"/>
     </row>
-    <row r="51" spans="1:16" s="45" customFormat="1" ht="71.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" s="45" customFormat="1" ht="71.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="26">
         <v>36</v>
       </c>
@@ -8237,7 +8239,7 @@
       <c r="O51" s="27"/>
       <c r="P51" s="27"/>
     </row>
-    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="30">
         <v>68</v>
       </c>
@@ -8265,7 +8267,7 @@
       </c>
       <c r="N52" s="30"/>
     </row>
-    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="26">
         <v>3</v>
       </c>
@@ -8303,7 +8305,7 @@
       </c>
       <c r="N53" s="26"/>
     </row>
-    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="26">
         <v>30</v>
       </c>
@@ -8343,7 +8345,7 @@
       </c>
       <c r="N54" s="26"/>
     </row>
-    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="26">
         <v>31</v>
       </c>
@@ -8383,7 +8385,7 @@
       </c>
       <c r="N55" s="26"/>
     </row>
-    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="26">
         <v>32</v>
       </c>
@@ -8421,7 +8423,7 @@
       </c>
       <c r="N56" s="26"/>
     </row>
-    <row r="57" spans="1:16" s="47" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="26">
         <v>56</v>
       </c>
@@ -8463,7 +8465,7 @@
       <c r="O57" s="27"/>
       <c r="P57" s="27"/>
     </row>
-    <row r="58" spans="1:16" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:16" ht="30" x14ac:dyDescent="0.25">
       <c r="A58" s="43">
         <v>57</v>
       </c>
@@ -8506,7 +8508,7 @@
       <c r="N58" s="26"/>
       <c r="O58" s="50"/>
     </row>
-    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="30">
         <v>62</v>
       </c>
@@ -8548,7 +8550,7 @@
       <c r="O59" s="30"/>
       <c r="P59" s="31"/>
     </row>
-    <row r="60" spans="1:16" s="87" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" s="87" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A60" s="85"/>
       <c r="B60" s="85" t="s">
         <v>81</v>
@@ -8568,11 +8570,11 @@
       <c r="G60" s="85" t="s">
         <v>487</v>
       </c>
-      <c r="H60" s="94" t="s">
+      <c r="H60" s="97" t="s">
         <v>495</v>
       </c>
-      <c r="I60" s="95"/>
-      <c r="J60" s="96"/>
+      <c r="I60" s="98"/>
+      <c r="J60" s="99"/>
       <c r="K60" s="85"/>
       <c r="L60" s="86" t="s">
         <v>440</v>
@@ -8582,7 +8584,7 @@
       </c>
       <c r="N60" s="85"/>
     </row>
-    <row r="61" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="57">
         <v>13</v>
       </c>
@@ -8620,7 +8622,7 @@
       <c r="O61" s="59"/>
       <c r="P61" s="59"/>
     </row>
-    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="57">
         <v>14</v>
       </c>
@@ -8658,7 +8660,7 @@
       <c r="O62" s="59"/>
       <c r="P62" s="59"/>
     </row>
-    <row r="63" spans="1:16" s="47" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" s="47" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="57">
         <v>15</v>
       </c>
@@ -8698,7 +8700,7 @@
       <c r="O63" s="59"/>
       <c r="P63" s="59"/>
     </row>
-    <row r="64" spans="1:16" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A64" s="26">
         <v>16</v>
       </c>
@@ -8736,7 +8738,7 @@
       <c r="O64" s="27"/>
       <c r="P64" s="27"/>
     </row>
-    <row r="65" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="26">
         <v>38</v>
       </c>
@@ -8776,7 +8778,7 @@
       </c>
       <c r="N65" s="26"/>
     </row>
-    <row r="66" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="26">
         <v>66</v>
       </c>
@@ -8805,7 +8807,7 @@
       <c r="N66" s="26"/>
       <c r="P66" s="11"/>
     </row>
-    <row r="67" spans="1:16" s="31" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" s="31" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="26">
         <v>4</v>
       </c>
@@ -8847,7 +8849,7 @@
       <c r="O67" s="27"/>
       <c r="P67" s="27"/>
     </row>
-    <row r="68" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="30">
         <v>8</v>
       </c>
@@ -8885,7 +8887,7 @@
       <c r="O68" s="31"/>
       <c r="P68" s="31"/>
     </row>
-    <row r="69" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="33">
         <v>61</v>
       </c>
@@ -8927,7 +8929,7 @@
       <c r="O69" s="47"/>
       <c r="P69" s="47"/>
     </row>
-    <row r="70" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="26">
         <v>69</v>
       </c>
@@ -8955,7 +8957,7 @@
       </c>
       <c r="N70" s="26"/>
     </row>
-    <row r="71" spans="1:16" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="1">
         <v>33</v>
       </c>
@@ -8983,7 +8985,7 @@
       <c r="O71" s="11"/>
       <c r="P71" s="11"/>
     </row>
-    <row r="72" spans="1:16" s="59" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" s="59" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1">
         <v>34</v>
       </c>
@@ -9011,7 +9013,7 @@
       <c r="O72" s="11"/>
       <c r="P72" s="11"/>
     </row>
-    <row r="73" spans="1:16" s="87" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" s="87" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="88"/>
       <c r="B73" s="89"/>
       <c r="C73" s="89" t="s">
@@ -9029,11 +9031,11 @@
       <c r="G73" s="89" t="s">
         <v>491</v>
       </c>
-      <c r="H73" s="94" t="s">
+      <c r="H73" s="97" t="s">
         <v>495</v>
       </c>
-      <c r="I73" s="95"/>
-      <c r="J73" s="96"/>
+      <c r="I73" s="98"/>
+      <c r="J73" s="99"/>
       <c r="K73" s="85"/>
       <c r="L73" s="85" t="s">
         <v>488</v>
@@ -9098,11 +9100,11 @@
       <c r="P76"/>
     </row>
     <row r="77" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A77" s="93" t="s">
+      <c r="A77" s="96" t="s">
         <v>461</v>
       </c>
-      <c r="B77" s="93"/>
-      <c r="C77" s="93"/>
+      <c r="B77" s="96"/>
+      <c r="C77" s="96"/>
       <c r="D77"/>
       <c r="E77"/>
       <c r="F77"/>
@@ -9173,7 +9175,7 @@
       </c>
       <c r="J81" s="49"/>
       <c r="K81" s="49"/>
-      <c r="L81" s="97"/>
+      <c r="L81" s="90"/>
       <c r="M81" s="49"/>
       <c r="N81" s="49"/>
     </row>
@@ -9203,9 +9205,9 @@
       <c r="C83" s="16">
         <v>27</v>
       </c>
-      <c r="J83" s="98"/>
-      <c r="K83" s="98"/>
-      <c r="L83" s="99"/>
+      <c r="J83" s="91"/>
+      <c r="K83" s="91"/>
+      <c r="L83" s="92"/>
       <c r="M83" s="49"/>
       <c r="N83" s="49"/>
     </row>
@@ -9245,11 +9247,11 @@
       <c r="N86" s="49"/>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A87" s="90" t="s">
+      <c r="A87" s="94" t="s">
         <v>462</v>
       </c>
-      <c r="B87" s="90"/>
-      <c r="C87" s="90"/>
+      <c r="B87" s="94"/>
+      <c r="C87" s="94"/>
       <c r="D87" s="54"/>
       <c r="J87" s="49"/>
       <c r="K87" s="49"/>
@@ -9271,7 +9273,7 @@
       <c r="J88" s="49"/>
       <c r="K88" s="49"/>
       <c r="L88" s="49"/>
-      <c r="M88" s="100"/>
+      <c r="M88" s="93"/>
       <c r="N88" s="49"/>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
@@ -9335,7 +9337,7 @@
       </c>
       <c r="D92" s="49"/>
       <c r="G92" s="49"/>
-      <c r="H92" s="97"/>
+      <c r="H92" s="90"/>
       <c r="I92" s="49"/>
       <c r="J92" s="49"/>
     </row>
@@ -9368,7 +9370,7 @@
       <c r="D94" s="49"/>
       <c r="G94" s="49"/>
       <c r="H94" s="49"/>
-      <c r="I94" s="99"/>
+      <c r="I94" s="92"/>
       <c r="J94" s="49"/>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
@@ -9382,11 +9384,11 @@
       <c r="A96" s="37"/>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" s="90" t="s">
+      <c r="A97" s="94" t="s">
         <v>463</v>
       </c>
-      <c r="B97" s="90"/>
-      <c r="C97" s="90"/>
+      <c r="B97" s="94"/>
+      <c r="C97" s="94"/>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="24" t="s">
@@ -9423,11 +9425,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A2:R73" xr:uid="{F96D30D7-88C4-4D8B-8E01-9968623D733C}">
-    <filterColumn colId="10">
-      <filters>
-        <filter val="SOLID WORDS 2022_x000a_ROBOTCUT-CAM_x000a_DISPRO SOLID FOR EDM"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:P72">
       <sortCondition ref="M2:M72"/>
     </sortState>

--- a/Kiem ke MT +PM Minh Thủy(Thống kê lại KASPER 3 nhà máy).xlsx
+++ b/Kiem ke MT +PM Minh Thủy(Thống kê lại KASPER 3 nhà máy).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PHAN MEM QLY TBI IT(Đang làm 22-10-2025)\QUANLY-IT-Cai-Tien-Update-PM-\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PHAN MEM QLY TBI IT(Đang làm 23-10-2025)\QUANLY-IT-Cai-Tien-Update-PM-\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1DFB5FE-D503-4C95-8676-1C6456F9EB69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEC2E00C-23C7-4E22-AA9D-C3DD975561CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2282,7 +2282,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5006B91-DE22-424D-8A0F-6DF1B14267DE}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A2:N67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -2344,7 +2343,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>1</v>
       </c>
@@ -2384,7 +2383,7 @@
       </c>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:14" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12">
         <v>2</v>
       </c>
@@ -2424,7 +2423,7 @@
       </c>
       <c r="N4" s="5"/>
     </row>
-    <row r="5" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>3</v>
       </c>
@@ -2464,7 +2463,7 @@
       </c>
       <c r="N5" s="1"/>
     </row>
-    <row r="6" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="12">
         <v>4</v>
       </c>
@@ -2504,7 +2503,7 @@
       </c>
       <c r="N6" s="1"/>
     </row>
-    <row r="7" spans="1:14" s="67" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="64">
         <v>5</v>
       </c>
@@ -2544,7 +2543,7 @@
       </c>
       <c r="N7" s="65"/>
     </row>
-    <row r="8" spans="1:14" s="67" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="64">
         <v>6</v>
       </c>
@@ -2584,7 +2583,7 @@
       </c>
       <c r="N8" s="65"/>
     </row>
-    <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="8">
         <v>7</v>
       </c>
@@ -2624,7 +2623,7 @@
       </c>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="12">
         <v>8</v>
       </c>
@@ -2664,7 +2663,7 @@
       </c>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="8">
         <v>9</v>
       </c>
@@ -2704,7 +2703,7 @@
       </c>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:14" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12">
         <v>10</v>
       </c>
@@ -2744,7 +2743,7 @@
       </c>
       <c r="N12" s="5"/>
     </row>
-    <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="8">
         <v>11</v>
       </c>
@@ -2784,7 +2783,7 @@
       </c>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="12">
         <v>12</v>
       </c>
@@ -2824,7 +2823,7 @@
       </c>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>13</v>
       </c>
@@ -2864,7 +2863,7 @@
       </c>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:14" s="7" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" s="7" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12">
         <v>14</v>
       </c>
@@ -2904,7 +2903,7 @@
       </c>
       <c r="N16" s="5"/>
     </row>
-    <row r="17" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="8">
         <v>15</v>
       </c>
@@ -2944,7 +2943,7 @@
       </c>
       <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="12">
         <v>16</v>
       </c>
@@ -2984,7 +2983,7 @@
       </c>
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="8">
         <v>17</v>
       </c>
@@ -3024,7 +3023,7 @@
       </c>
       <c r="N19" s="1"/>
     </row>
-    <row r="20" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="12">
         <v>18</v>
       </c>
@@ -3064,7 +3063,7 @@
       </c>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="8">
         <v>19</v>
       </c>
@@ -3104,7 +3103,7 @@
       </c>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="68">
         <v>20</v>
       </c>
@@ -3144,7 +3143,7 @@
       </c>
       <c r="N22" s="69"/>
     </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -3182,7 +3181,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -3220,7 +3219,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="72">
         <v>23</v>
       </c>
@@ -3260,7 +3259,7 @@
       </c>
       <c r="N25" s="73"/>
     </row>
-    <row r="26" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="12">
         <v>24</v>
       </c>
@@ -3300,7 +3299,7 @@
       </c>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="8">
         <v>25</v>
       </c>
@@ -3340,7 +3339,7 @@
       </c>
       <c r="N27" s="1"/>
     </row>
-    <row r="28" spans="1:14" s="59" customFormat="1" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" s="59" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="56">
         <v>26</v>
       </c>
@@ -3452,7 +3451,7 @@
       </c>
       <c r="N30" s="57"/>
     </row>
-    <row r="31" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="60">
         <v>29</v>
       </c>
@@ -3480,7 +3479,7 @@
       </c>
       <c r="N31" s="61"/>
     </row>
-    <row r="32" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="60">
         <v>30</v>
       </c>
@@ -3508,7 +3507,7 @@
       </c>
       <c r="N32" s="61"/>
     </row>
-    <row r="33" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="60">
         <v>31</v>
       </c>
@@ -3536,7 +3535,7 @@
       </c>
       <c r="N33" s="61"/>
     </row>
-    <row r="34" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="60">
         <v>32</v>
       </c>
@@ -3564,7 +3563,7 @@
       </c>
       <c r="N34" s="61"/>
     </row>
-    <row r="35" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="60">
         <v>33</v>
       </c>
@@ -3592,7 +3591,7 @@
       </c>
       <c r="N35" s="61"/>
     </row>
-    <row r="36" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="60">
         <v>34</v>
       </c>
@@ -3620,7 +3619,7 @@
       </c>
       <c r="N36" s="61"/>
     </row>
-    <row r="37" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="60">
         <v>35</v>
       </c>
@@ -3648,7 +3647,7 @@
       </c>
       <c r="N37" s="61"/>
     </row>
-    <row r="38" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="60">
         <v>36</v>
       </c>
@@ -3975,13 +3974,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:N38" xr:uid="{083D8963-DEF1-4333-BE50-8D9BD074B1F1}">
-    <filterColumn colId="12">
-      <filters>
-        <filter val="IT"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A2:N38" xr:uid="{083D8963-DEF1-4333-BE50-8D9BD074B1F1}"/>
   <mergeCells count="3">
     <mergeCell ref="A64:C64"/>
     <mergeCell ref="A39:N39"/>
